--- a/output/yearly_benthic_cover_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_96_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.17581432842437</v>
+        <v>45.26071859563213</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6384940961121</v>
+        <v>100.4631328093314</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03762175947625</v>
+        <v>88.01544407883732</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88191118104993</v>
+        <v>45.92018338811537</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228792539137711</v>
+        <v>2.228706623205536</v>
       </c>
       <c r="E3" t="n">
-        <v>5.680395789525059</v>
+        <v>5.700852541837528</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742930846379237</v>
+        <v>0.7429022077351788</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95673970900099</v>
+        <v>33.97029565051574</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1748189334449</v>
+        <v>34.17350155581822</v>
       </c>
       <c r="I3" t="n">
-        <v>6.610626152118118</v>
+        <v>6.556046701380253</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643317789870231</v>
+        <v>4.643138798344867</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96237824052374</v>
+        <v>11.98455592116268</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91842959202548</v>
+        <v>48.85992970069867</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7627190135992</v>
+        <v>106.7646690099767</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22810771510235</v>
+        <v>87.09604757251817</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71748736079659</v>
+        <v>42.6339225588332</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190307834436688</v>
+        <v>2.184370134327024</v>
       </c>
       <c r="E4" t="n">
-        <v>6.502391457615939</v>
+        <v>6.499913323892728</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744498128776701</v>
+        <v>0.7444588247492373</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37040649163659</v>
+        <v>33.2945119382824</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24691392372824</v>
+        <v>34.24510593846491</v>
       </c>
       <c r="I4" t="n">
-        <v>5.520476574053816</v>
+        <v>5.474819758119132</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653113304854381</v>
+        <v>4.652867654682733</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77189228489766</v>
+        <v>12.90395242748183</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32699185008023</v>
+        <v>44.2800126053133</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81637149577448</v>
+        <v>99.81788759162832</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.1273671253703</v>
+        <v>85.89730847904565</v>
       </c>
       <c r="C5" t="n">
-        <v>42.47359618024135</v>
+        <v>42.28490676085099</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136794611553658</v>
+        <v>2.125757227641166</v>
       </c>
       <c r="E5" t="n">
-        <v>7.11162658381353</v>
+        <v>7.087242302695087</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458260442888717</v>
+        <v>0.7457792020122049</v>
       </c>
       <c r="G5" t="n">
-        <v>32.55510648119603</v>
+        <v>32.40112482832224</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30799803728809</v>
+        <v>34.30584329256142</v>
       </c>
       <c r="I5" t="n">
-        <v>4.608602590424661</v>
+        <v>4.570441613237256</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661412776805448</v>
+        <v>4.66112001257628</v>
       </c>
       <c r="K5" t="n">
-        <v>13.8726328746297</v>
+        <v>14.10269152095434</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50042437362747</v>
+        <v>43.46032339158025</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84665342849853</v>
+        <v>99.84792167338558</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.91852456052463</v>
+        <v>84.49478533939134</v>
       </c>
       <c r="C6" t="n">
-        <v>41.98059484912093</v>
+        <v>41.59216397841043</v>
       </c>
       <c r="D6" t="n">
-        <v>2.078137255313317</v>
+        <v>2.057203742865431</v>
       </c>
       <c r="E6" t="n">
-        <v>7.55745472403582</v>
+        <v>7.494424805622978</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469520927136605</v>
+        <v>0.7469014505815542</v>
       </c>
       <c r="G6" t="n">
-        <v>31.66143309397175</v>
+        <v>31.3562218691542</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35979626482838</v>
+        <v>34.35746672675149</v>
       </c>
       <c r="I6" t="n">
-        <v>3.846300550201302</v>
+        <v>3.814432678280986</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668450579460378</v>
+        <v>4.668134066134713</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08147543947539</v>
+        <v>15.50521466060867</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80991297278076</v>
+        <v>42.77566464950208</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87198326137708</v>
+        <v>99.87304328852116</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.52486345791453</v>
+        <v>82.82122935211183</v>
       </c>
       <c r="C7" t="n">
-        <v>41.18452447317465</v>
+        <v>40.51097819737258</v>
       </c>
       <c r="D7" t="n">
-        <v>2.010577685115745</v>
+        <v>1.975570166625994</v>
       </c>
       <c r="E7" t="n">
-        <v>7.846656937796522</v>
+        <v>7.727493390651613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479087878764391</v>
+        <v>0.7478582150745258</v>
       </c>
       <c r="G7" t="n">
-        <v>30.63213014191751</v>
+        <v>30.11195010588639</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4038042423162</v>
+        <v>34.40147789342818</v>
       </c>
       <c r="I7" t="n">
-        <v>3.20935573866437</v>
+        <v>3.182765736229347</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674429924227745</v>
+        <v>4.674113844215785</v>
       </c>
       <c r="K7" t="n">
-        <v>16.47513654208548</v>
+        <v>17.17877064788816</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23349730278984</v>
+        <v>42.20429469145369</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89315831804997</v>
+        <v>99.89404353671443</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.1985807639381</v>
+        <v>87.53770957623853</v>
       </c>
       <c r="C8" t="n">
-        <v>43.42566666074661</v>
+        <v>42.71345792391234</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0147740416134</v>
+        <v>1.979764116082543</v>
       </c>
       <c r="E8" t="n">
-        <v>9.631812332090075</v>
+        <v>9.490389682178538</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494697779962901</v>
+        <v>0.7494458476515273</v>
       </c>
       <c r="G8" t="n">
-        <v>31.12024594174157</v>
+        <v>30.58453492754303</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47560978782934</v>
+        <v>34.47450899197025</v>
       </c>
       <c r="I8" t="n">
-        <v>5.522482770190601</v>
+        <v>5.575029462990583</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684186112476814</v>
+        <v>4.684036547822045</v>
       </c>
       <c r="K8" t="n">
-        <v>11.80141923606191</v>
+        <v>12.46229042376149</v>
       </c>
       <c r="L8" t="n">
-        <v>44.58921475039641</v>
+        <v>44.63881100991706</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81630064720493</v>
+        <v>99.81455935759089</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.16264219778135</v>
+        <v>85.26592272212733</v>
       </c>
       <c r="C9" t="n">
-        <v>42.24737502314441</v>
+        <v>41.30665736698204</v>
       </c>
       <c r="D9" t="n">
-        <v>1.922282009266613</v>
+        <v>1.876225251792229</v>
       </c>
       <c r="E9" t="n">
-        <v>9.958025181323492</v>
+        <v>9.769774244728088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508064993443692</v>
+        <v>0.7508094851031449</v>
       </c>
       <c r="G9" t="n">
-        <v>29.69161189403538</v>
+        <v>28.98500699109809</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53709896984098</v>
+        <v>34.53723631474466</v>
       </c>
       <c r="I9" t="n">
-        <v>4.610277023068217</v>
+        <v>4.654311152766462</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692540620902308</v>
+        <v>4.692559281894655</v>
       </c>
       <c r="K9" t="n">
-        <v>13.83735780221864</v>
+        <v>14.73407727787267</v>
       </c>
       <c r="L9" t="n">
-        <v>43.76186487546499</v>
+        <v>43.80440342561779</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84659770082804</v>
+        <v>99.8451380704725</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.79967094892586</v>
+        <v>82.90139984367509</v>
       </c>
       <c r="C10" t="n">
-        <v>40.60007058831827</v>
+        <v>39.66372519882025</v>
       </c>
       <c r="D10" t="n">
-        <v>1.81579332754481</v>
+        <v>1.769798292504441</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04767661625884</v>
+        <v>9.863035591847556</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519556432840313</v>
+        <v>0.7519822166802475</v>
       </c>
       <c r="G10" t="n">
-        <v>28.04678527986052</v>
+        <v>27.34086210175116</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58995959106544</v>
+        <v>34.59118196729138</v>
       </c>
       <c r="I10" t="n">
-        <v>3.847777720387028</v>
+        <v>3.884650819348781</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699722770525197</v>
+        <v>4.699888854251546</v>
       </c>
       <c r="K10" t="n">
-        <v>16.20032905107414</v>
+        <v>17.09860015632487</v>
       </c>
       <c r="L10" t="n">
-        <v>43.0715371099668</v>
+        <v>43.1083882239447</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87193674935921</v>
+        <v>99.87071357908982</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.34094781706504</v>
+        <v>80.39580501656594</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73790130736337</v>
+        <v>37.75961821169486</v>
       </c>
       <c r="D11" t="n">
-        <v>1.706170943678039</v>
+        <v>1.658244744383143</v>
       </c>
       <c r="E11" t="n">
-        <v>9.976198827002955</v>
+        <v>9.781610809236632</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529450196029754</v>
+        <v>0.752992881081295</v>
       </c>
       <c r="G11" t="n">
-        <v>26.35355543066014</v>
+        <v>25.6175187190262</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63547090173687</v>
+        <v>34.63767252973957</v>
       </c>
       <c r="I11" t="n">
-        <v>3.210700321865457</v>
+        <v>3.241559826341001</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705906372518598</v>
+        <v>4.706205506758094</v>
       </c>
       <c r="K11" t="n">
-        <v>18.65905218293495</v>
+        <v>19.60419498343408</v>
       </c>
       <c r="L11" t="n">
-        <v>42.4961637952465</v>
+        <v>42.52827983766691</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89311728554482</v>
+        <v>99.89209303279586</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.81506006485968</v>
+        <v>77.75361661426871</v>
       </c>
       <c r="C12" t="n">
-        <v>36.70891306899784</v>
+        <v>35.61839539397743</v>
       </c>
       <c r="D12" t="n">
-        <v>1.59467214267863</v>
+        <v>1.541797494274027</v>
       </c>
       <c r="E12" t="n">
-        <v>9.770686916988543</v>
+        <v>9.545453434955865</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537980078461775</v>
+        <v>0.7538659027887434</v>
       </c>
       <c r="G12" t="n">
-        <v>24.63134239949943</v>
+        <v>23.81857461288396</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67470836092416</v>
+        <v>34.6778315282822</v>
       </c>
       <c r="I12" t="n">
-        <v>2.678614687884109</v>
+        <v>2.704431748654267</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711237549038611</v>
+        <v>4.711661892429647</v>
       </c>
       <c r="K12" t="n">
-        <v>21.18493993514032</v>
+        <v>22.24638338573128</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01696087581002</v>
+        <v>42.04517789178183</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91081387994818</v>
+        <v>99.90995667149055</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.29047421264009</v>
+        <v>75.21799482958984</v>
       </c>
       <c r="C13" t="n">
-        <v>34.59794343255487</v>
+        <v>33.49968518087016</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484279323197186</v>
+        <v>1.431227980896867</v>
       </c>
       <c r="E13" t="n">
-        <v>9.466694076269794</v>
+        <v>9.236895337170237</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545339034176248</v>
+        <v>0.7546195703744277</v>
       </c>
       <c r="G13" t="n">
-        <v>22.92621238416841</v>
+        <v>22.11043316495391</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70855955721074</v>
+        <v>34.71250023722368</v>
       </c>
       <c r="I13" t="n">
-        <v>2.234358072016172</v>
+        <v>2.255946224130555</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715836896360156</v>
+        <v>4.716372314840174</v>
       </c>
       <c r="K13" t="n">
-        <v>23.70952578735991</v>
+        <v>24.78200517041014</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61812481653287</v>
+        <v>41.6431865445904</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92559403644765</v>
+        <v>99.92487689587071</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.27463195118601</v>
+        <v>82.42792364365833</v>
       </c>
       <c r="C14" t="n">
-        <v>39.06920627775494</v>
+        <v>38.08990990873723</v>
       </c>
       <c r="D14" t="n">
-        <v>1.485883509381615</v>
+        <v>1.432832555091861</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92307165440143</v>
+        <v>11.75920061386914</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553493920151066</v>
+        <v>0.755465587295437</v>
       </c>
       <c r="G14" t="n">
-        <v>24.94712711711514</v>
+        <v>24.18511440265826</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7422084691356</v>
+        <v>36.80130986809645</v>
       </c>
       <c r="I14" t="n">
-        <v>2.70005810904268</v>
+        <v>2.772340696050696</v>
       </c>
       <c r="J14" t="n">
-        <v>4.720933700094418</v>
+        <v>4.721659920596482</v>
       </c>
       <c r="K14" t="n">
-        <v>16.72536804881402</v>
+        <v>17.57207635634168</v>
       </c>
       <c r="L14" t="n">
-        <v>44.11552090415</v>
+        <v>44.24570586631804</v>
       </c>
       <c r="M14" t="n">
-        <v>99.91009523071897</v>
+        <v>99.90769213139696</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.3247714123731</v>
+        <v>81.56240505011729</v>
       </c>
       <c r="C15" t="n">
-        <v>38.53657920480079</v>
+        <v>37.6521418842696</v>
       </c>
       <c r="D15" t="n">
-        <v>1.450408070501249</v>
+        <v>1.400976143589929</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01375859029116</v>
+        <v>11.88316750926967</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560381772090327</v>
+        <v>0.7561795557233082</v>
       </c>
       <c r="G15" t="n">
-        <v>24.35151495930053</v>
+        <v>23.64740261359091</v>
       </c>
       <c r="H15" t="n">
-        <v>36.77571281752486</v>
+        <v>36.83608970955051</v>
       </c>
       <c r="I15" t="n">
-        <v>2.252100189989815</v>
+        <v>2.312467295122291</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725238607556455</v>
+        <v>4.726122223270678</v>
       </c>
       <c r="K15" t="n">
-        <v>17.67522858762689</v>
+        <v>18.43759494988271</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71319059343226</v>
+        <v>43.83325370206851</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92499838585994</v>
+        <v>99.92299053622082</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.76437339969743</v>
+        <v>78.94078525060478</v>
       </c>
       <c r="C16" t="n">
-        <v>36.32411347768043</v>
+        <v>35.38728203587274</v>
       </c>
       <c r="D16" t="n">
-        <v>1.353266196259345</v>
+        <v>1.30258649527661</v>
       </c>
       <c r="E16" t="n">
-        <v>11.52216773906826</v>
+        <v>11.37005791335553</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7566315952165938</v>
+        <v>0.7567953705246185</v>
       </c>
       <c r="G16" t="n">
-        <v>22.72055891879896</v>
+        <v>21.98666082486014</v>
       </c>
       <c r="H16" t="n">
-        <v>36.80457825168504</v>
+        <v>36.86608815250476</v>
       </c>
       <c r="I16" t="n">
-        <v>1.878223228565497</v>
+        <v>1.928625428304247</v>
       </c>
       <c r="J16" t="n">
-        <v>4.728947470103712</v>
+        <v>4.729971065778868</v>
       </c>
       <c r="K16" t="n">
-        <v>20.23562660030258</v>
+        <v>21.05921474939523</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37770158340616</v>
+        <v>43.48926801208976</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93744166138917</v>
+        <v>99.93576479735772</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.3027818697292</v>
+        <v>80.73128689613306</v>
       </c>
       <c r="C17" t="n">
-        <v>37.46755747487648</v>
+        <v>36.6963031187173</v>
       </c>
       <c r="D17" t="n">
-        <v>1.354285642428702</v>
+        <v>1.303605668510806</v>
       </c>
       <c r="E17" t="n">
-        <v>12.24185219632364</v>
+        <v>12.17747116915832</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572015829865466</v>
+        <v>0.757387504396879</v>
       </c>
       <c r="G17" t="n">
-        <v>23.14244321537731</v>
+        <v>22.4865507969802</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23707235998983</v>
+        <v>37.37762012623276</v>
       </c>
       <c r="I17" t="n">
-        <v>1.837416978957269</v>
+        <v>1.894979728373602</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732509893665917</v>
+        <v>4.733671902480496</v>
       </c>
       <c r="K17" t="n">
-        <v>18.69721813027078</v>
+        <v>19.26871310386694</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77402326642125</v>
+        <v>43.9718671703357</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93879887156851</v>
+        <v>99.93688339291992</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.87785522276256</v>
+        <v>78.13748982655892</v>
       </c>
       <c r="C18" t="n">
-        <v>35.32605279278249</v>
+        <v>34.39440969841282</v>
       </c>
       <c r="D18" t="n">
-        <v>1.265715147930656</v>
+        <v>1.210411859606012</v>
       </c>
       <c r="E18" t="n">
-        <v>11.6965951722525</v>
+        <v>11.57028177703687</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7576918613792816</v>
+        <v>0.7578980721886859</v>
       </c>
       <c r="G18" t="n">
-        <v>21.62892378102591</v>
+        <v>20.87900384584146</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26118289065566</v>
+        <v>37.40281701535499</v>
       </c>
       <c r="I18" t="n">
-        <v>1.532172235898029</v>
+        <v>1.580214305351597</v>
       </c>
       <c r="J18" t="n">
-        <v>4.735574133620511</v>
+        <v>4.736862951179289</v>
       </c>
       <c r="K18" t="n">
-        <v>21.12214477723744</v>
+        <v>21.86251017344109</v>
       </c>
       <c r="L18" t="n">
-        <v>43.50076306945347</v>
+        <v>43.69044180235792</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9489606394734</v>
+        <v>99.94736167421185</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.88343315565393</v>
+        <v>77.0918008943345</v>
       </c>
       <c r="C19" t="n">
-        <v>34.55513192337733</v>
+        <v>33.58120228949376</v>
       </c>
       <c r="D19" t="n">
-        <v>1.229489395799365</v>
+        <v>1.173056458366279</v>
       </c>
       <c r="E19" t="n">
-        <v>11.57671322376237</v>
+        <v>11.43444571502492</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581099621926192</v>
+        <v>0.7583330847522038</v>
       </c>
       <c r="G19" t="n">
-        <v>21.0098871573124</v>
+        <v>20.23464171409467</v>
       </c>
       <c r="H19" t="n">
-        <v>37.281743928284</v>
+        <v>37.42428519941522</v>
       </c>
       <c r="I19" t="n">
-        <v>1.289302224599294</v>
+        <v>1.327456942979914</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738187263703871</v>
+        <v>4.739581779701276</v>
       </c>
       <c r="K19" t="n">
-        <v>22.11656684434608</v>
+        <v>22.9081991056655</v>
       </c>
       <c r="L19" t="n">
-        <v>43.28534819330883</v>
+        <v>43.46637542295989</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95704696103225</v>
+        <v>99.95577681811915</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.28912557727355</v>
+        <v>74.31770585887541</v>
       </c>
       <c r="C20" t="n">
-        <v>32.15896191410295</v>
+        <v>31.01075095663732</v>
       </c>
       <c r="D20" t="n">
-        <v>1.135705492424363</v>
+        <v>1.074504398330038</v>
       </c>
       <c r="E20" t="n">
-        <v>10.87281108719435</v>
+        <v>10.65826350891105</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7584707557871021</v>
+        <v>0.7587095294518502</v>
       </c>
       <c r="G20" t="n">
-        <v>19.40727941314394</v>
+        <v>18.53466759026045</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29948675593604</v>
+        <v>37.44286301711122</v>
       </c>
       <c r="I20" t="n">
-        <v>1.074929849118375</v>
+        <v>1.106763255736741</v>
       </c>
       <c r="J20" t="n">
-        <v>4.740442223669389</v>
+        <v>4.741934559074066</v>
       </c>
       <c r="K20" t="n">
-        <v>24.71087442272645</v>
+        <v>25.68229414112458</v>
       </c>
       <c r="L20" t="n">
-        <v>43.09434971248729</v>
+        <v>43.27008109826642</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96418604931668</v>
+        <v>99.96312619602833</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.3581917101569</v>
+        <v>80.51860107348502</v>
       </c>
       <c r="C21" t="n">
-        <v>36.03476605064419</v>
+        <v>34.95508076728571</v>
       </c>
       <c r="D21" t="n">
-        <v>1.136368701099581</v>
+        <v>1.075167015264974</v>
       </c>
       <c r="E21" t="n">
-        <v>12.92931243664654</v>
+        <v>12.75464941256209</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7589136737693538</v>
+        <v>0.7591774044867905</v>
       </c>
       <c r="G21" t="n">
-        <v>21.23121416761117</v>
+        <v>20.38764275969854</v>
       </c>
       <c r="H21" t="n">
-        <v>39.13386987682193</v>
+        <v>39.30749834403063</v>
       </c>
       <c r="I21" t="n">
-        <v>1.425302393149869</v>
+        <v>1.48960735939956</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743210461058463</v>
+        <v>4.744858778042442</v>
       </c>
       <c r="K21" t="n">
-        <v>18.64180828984309</v>
+        <v>19.48139892651497</v>
       </c>
       <c r="L21" t="n">
-        <v>45.2759433076229</v>
+        <v>45.51389732866081</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95251764811019</v>
+        <v>99.95037702246148</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_96_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.26071859563213</v>
+        <v>45.32497404946396</v>
       </c>
       <c r="M2" t="n">
-        <v>100.4631328093314</v>
+        <v>100.0264200128927</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01544407883732</v>
+        <v>88.02310171093043</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92018338811537</v>
+        <v>45.94297568372332</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228706623205536</v>
+        <v>2.228708982292671</v>
       </c>
       <c r="E3" t="n">
-        <v>5.700852541837528</v>
+        <v>5.714213346005715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429022077351788</v>
+        <v>0.7429029940975571</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97029565051574</v>
+        <v>33.97814241909069</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17350155581822</v>
+        <v>34.17353772848762</v>
       </c>
       <c r="I3" t="n">
-        <v>6.556046701380253</v>
+        <v>6.542452527846453</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643138798344867</v>
+        <v>4.643143713109732</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98455592116268</v>
+        <v>11.97689828906955</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85992970069867</v>
+        <v>48.84528325213594</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646690099767</v>
+        <v>106.7651572249288</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09604757251817</v>
+        <v>87.0134251521277</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6339225588332</v>
+        <v>42.56296514488478</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184370134327024</v>
+        <v>2.179582355778925</v>
       </c>
       <c r="E4" t="n">
-        <v>6.499913323892728</v>
+        <v>6.498832782283176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444588247492373</v>
+        <v>0.7444578563935259</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2945119382824</v>
+        <v>33.22917450739126</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24510593846491</v>
+        <v>34.24506139410219</v>
       </c>
       <c r="I4" t="n">
-        <v>5.474819758119132</v>
+        <v>5.463454653719092</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652867654682733</v>
+        <v>4.652861602459536</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90395242748183</v>
+        <v>12.9865748478723</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2800126053133</v>
+        <v>44.26872521480273</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81788759162832</v>
+        <v>99.81826520755982</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.89730847904565</v>
+        <v>85.82436264286888</v>
       </c>
       <c r="C5" t="n">
-        <v>42.28490676085099</v>
+        <v>42.22179813893793</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125757227641166</v>
+        <v>2.121491523926747</v>
       </c>
       <c r="E5" t="n">
-        <v>7.087242302695087</v>
+        <v>7.0857814206083</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457792020122049</v>
+        <v>0.7457766080323117</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40112482832224</v>
+        <v>32.34354135672018</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30584329256142</v>
+        <v>34.30572396948634</v>
       </c>
       <c r="I5" t="n">
-        <v>4.570441613237256</v>
+        <v>4.560943963893049</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66112001257628</v>
+        <v>4.661103800201947</v>
       </c>
       <c r="K5" t="n">
-        <v>14.10269152095434</v>
+        <v>14.17563735713113</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46032339158025</v>
+        <v>43.45080187466097</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84792167338558</v>
+        <v>99.84823737073002</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.49478533939134</v>
+        <v>84.24329228596267</v>
       </c>
       <c r="C6" t="n">
-        <v>41.59216397841043</v>
+        <v>41.34898499181093</v>
       </c>
       <c r="D6" t="n">
-        <v>2.057203742865431</v>
+        <v>2.043839327780948</v>
       </c>
       <c r="E6" t="n">
-        <v>7.494424805622978</v>
+        <v>7.460841632292173</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469014505815542</v>
+        <v>0.7468998654258047</v>
       </c>
       <c r="G6" t="n">
-        <v>31.3562218691542</v>
+        <v>31.15968227024453</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35746672675149</v>
+        <v>34.35739380958701</v>
       </c>
       <c r="I6" t="n">
-        <v>3.814432678280986</v>
+        <v>3.806511221720925</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668134066134713</v>
+        <v>4.668124158911278</v>
       </c>
       <c r="K6" t="n">
-        <v>15.50521466060867</v>
+        <v>15.75670771403733</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77566464950208</v>
+        <v>42.76761440626583</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87304328852116</v>
+        <v>99.87330711211409</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.82122935211183</v>
+        <v>82.54620925589816</v>
       </c>
       <c r="C7" t="n">
-        <v>40.51097819737258</v>
+        <v>40.24286217980686</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975570166625994</v>
+        <v>1.961053898255083</v>
       </c>
       <c r="E7" t="n">
-        <v>7.727493390651613</v>
+        <v>7.688001463746533</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478582150745258</v>
+        <v>0.7478578235410976</v>
       </c>
       <c r="G7" t="n">
-        <v>30.11195010588639</v>
+        <v>29.89756364596285</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40147789342818</v>
+        <v>34.40145988289049</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182765736229347</v>
+        <v>3.176161144370254</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674113844215785</v>
+        <v>4.674111397131859</v>
       </c>
       <c r="K7" t="n">
-        <v>17.17877064788816</v>
+        <v>17.45379074410183</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20429469145369</v>
+        <v>42.19761065326572</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89404353671443</v>
+        <v>99.89426357717441</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.53770957623853</v>
+        <v>87.40522777055082</v>
       </c>
       <c r="C8" t="n">
-        <v>42.71345792391234</v>
+        <v>42.52797187313445</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979764116082543</v>
+        <v>1.965261895507815</v>
       </c>
       <c r="E8" t="n">
-        <v>9.490389682178538</v>
+        <v>9.509277847591511</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494458476515273</v>
+        <v>0.7494625645784017</v>
       </c>
       <c r="G8" t="n">
-        <v>30.58453492754303</v>
+        <v>30.39522538915726</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47450899197025</v>
+        <v>34.47527797060647</v>
       </c>
       <c r="I8" t="n">
-        <v>5.575029462990583</v>
+        <v>5.626581074494349</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684036547822045</v>
+        <v>4.684141028615009</v>
       </c>
       <c r="K8" t="n">
-        <v>12.46229042376149</v>
+        <v>12.59477222944919</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63881100991706</v>
+        <v>44.69010478072622</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81455935759089</v>
+        <v>99.81284888330985</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.26592272212733</v>
+        <v>85.24228797527562</v>
       </c>
       <c r="C9" t="n">
-        <v>41.30665736698204</v>
+        <v>41.23775749523958</v>
       </c>
       <c r="D9" t="n">
-        <v>1.876225251792229</v>
+        <v>1.867162409588013</v>
       </c>
       <c r="E9" t="n">
-        <v>9.769774244728088</v>
+        <v>9.817510676659559</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508094851031449</v>
+        <v>0.7508392475737958</v>
       </c>
       <c r="G9" t="n">
-        <v>28.98500699109809</v>
+        <v>28.87799453462916</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53723631474466</v>
+        <v>34.5386053883946</v>
       </c>
       <c r="I9" t="n">
-        <v>4.654311152766462</v>
+        <v>4.697430421094271</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692559281894655</v>
+        <v>4.692745297336223</v>
       </c>
       <c r="K9" t="n">
-        <v>14.73407727787267</v>
+        <v>14.75771202472437</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80440342561779</v>
+        <v>43.84823656130011</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8451380704725</v>
+        <v>99.84370608126405</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.90139984367509</v>
+        <v>82.9546561224513</v>
       </c>
       <c r="C10" t="n">
-        <v>39.66372519882025</v>
+        <v>39.67829590744485</v>
       </c>
       <c r="D10" t="n">
-        <v>1.769798292504441</v>
+        <v>1.764634868856695</v>
       </c>
       <c r="E10" t="n">
-        <v>9.863035591847556</v>
+        <v>9.931871214047055</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519822166802475</v>
+        <v>0.7520221467203041</v>
       </c>
       <c r="G10" t="n">
-        <v>27.34086210175116</v>
+        <v>27.29227829179773</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59118196729138</v>
+        <v>34.59301874913398</v>
       </c>
       <c r="I10" t="n">
-        <v>3.884650819348781</v>
+        <v>3.920692434893639</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699888854251546</v>
+        <v>4.700138417001899</v>
       </c>
       <c r="K10" t="n">
-        <v>17.09860015632487</v>
+        <v>17.0453438775487</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1083882239447</v>
+        <v>43.14587603664272</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87071357908982</v>
+        <v>99.86951582163627</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.39580501656594</v>
+        <v>80.4666698485548</v>
       </c>
       <c r="C11" t="n">
-        <v>37.75961821169486</v>
+        <v>37.79736086348274</v>
       </c>
       <c r="D11" t="n">
-        <v>1.658244744383143</v>
+        <v>1.654267430045098</v>
       </c>
       <c r="E11" t="n">
-        <v>9.781610809236632</v>
+        <v>9.855970237116342</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752992881081295</v>
+        <v>0.7530413553050038</v>
       </c>
       <c r="G11" t="n">
-        <v>25.6175187190262</v>
+        <v>25.58530825082226</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63767252973957</v>
+        <v>34.63990234403016</v>
       </c>
       <c r="I11" t="n">
-        <v>3.241559826341001</v>
+        <v>3.271671760579667</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706205506758094</v>
+        <v>4.706508470656273</v>
       </c>
       <c r="K11" t="n">
-        <v>19.60419498343408</v>
+        <v>19.53333015144519</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52827983766691</v>
+        <v>42.56040086188057</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89209303279586</v>
+        <v>99.8910918768085</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.75361661426871</v>
+        <v>77.98894512339831</v>
       </c>
       <c r="C12" t="n">
-        <v>35.61839539397743</v>
+        <v>35.82526140376828</v>
       </c>
       <c r="D12" t="n">
-        <v>1.541797494274027</v>
+        <v>1.545574903309589</v>
       </c>
       <c r="E12" t="n">
-        <v>9.545453434955865</v>
+        <v>9.66331933431721</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538659027887434</v>
+        <v>0.7539198909362799</v>
       </c>
       <c r="G12" t="n">
-        <v>23.81857461288396</v>
+        <v>23.90424281328722</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6778315282822</v>
+        <v>34.68031498306886</v>
       </c>
       <c r="I12" t="n">
-        <v>2.704431748654267</v>
+        <v>2.729573880127398</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711661892429647</v>
+        <v>4.711999318351747</v>
       </c>
       <c r="K12" t="n">
-        <v>22.24638338573128</v>
+        <v>22.01105487660168</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04517789178183</v>
+        <v>42.07280394850282</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90995667149055</v>
+        <v>99.90912022887278</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.21799482958984</v>
+        <v>75.58233077058007</v>
       </c>
       <c r="C13" t="n">
-        <v>33.49968518087016</v>
+        <v>33.83955007238308</v>
       </c>
       <c r="D13" t="n">
-        <v>1.431227980896867</v>
+        <v>1.441088611448453</v>
       </c>
       <c r="E13" t="n">
-        <v>9.236895337170237</v>
+        <v>9.389533179965891</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546195703744277</v>
+        <v>0.754676955923788</v>
       </c>
       <c r="G13" t="n">
-        <v>22.11043316495391</v>
+        <v>22.28823204217527</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71250023722368</v>
+        <v>34.71513997249424</v>
       </c>
       <c r="I13" t="n">
-        <v>2.255946224130555</v>
+        <v>2.276929034048759</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716372314840174</v>
+        <v>4.716730974523673</v>
       </c>
       <c r="K13" t="n">
-        <v>24.78200517041014</v>
+        <v>24.41766922941993</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6431865445904</v>
+        <v>41.66695920152678</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92487689587071</v>
+        <v>99.92417850332978</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.42792364365833</v>
+        <v>82.91912147252413</v>
       </c>
       <c r="C14" t="n">
-        <v>38.08990990873723</v>
+        <v>38.29243609150397</v>
       </c>
       <c r="D14" t="n">
-        <v>1.432832555091861</v>
+        <v>1.442911403316687</v>
       </c>
       <c r="E14" t="n">
-        <v>11.75920061386914</v>
+        <v>11.87586213456655</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755465587295437</v>
+        <v>0.7556315252732878</v>
       </c>
       <c r="G14" t="n">
-        <v>24.18511440265826</v>
+        <v>24.26646603821983</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80130986809645</v>
+        <v>36.70909240982182</v>
       </c>
       <c r="I14" t="n">
-        <v>2.772340696050696</v>
+        <v>3.146460928367901</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721659920596482</v>
+        <v>4.722697032958047</v>
       </c>
       <c r="K14" t="n">
-        <v>17.57207635634168</v>
+        <v>17.08087852747587</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24570586631804</v>
+        <v>44.5219358447743</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90769213139696</v>
+        <v>99.89525046375414</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.56240505011729</v>
+        <v>82.17984581627219</v>
       </c>
       <c r="C15" t="n">
-        <v>37.6521418842696</v>
+        <v>38.02913331454411</v>
       </c>
       <c r="D15" t="n">
-        <v>1.400976143589929</v>
+        <v>1.414944448012835</v>
       </c>
       <c r="E15" t="n">
-        <v>11.88316750926967</v>
+        <v>12.09263490966493</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561795557233082</v>
+        <v>0.7564360265265502</v>
       </c>
       <c r="G15" t="n">
-        <v>23.64740261359091</v>
+        <v>23.80560656056333</v>
       </c>
       <c r="H15" t="n">
-        <v>36.83608970955051</v>
+        <v>36.75765630273722</v>
       </c>
       <c r="I15" t="n">
-        <v>2.312467295122291</v>
+        <v>2.624842402976382</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726122223270678</v>
+        <v>4.727725165790937</v>
       </c>
       <c r="K15" t="n">
-        <v>18.43759494988271</v>
+        <v>17.82015418372781</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83325370206851</v>
+        <v>44.06331080927342</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92299053622082</v>
+        <v>99.91259830754534</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.94078525060478</v>
+        <v>79.69254873765473</v>
       </c>
       <c r="C16" t="n">
-        <v>35.38728203587274</v>
+        <v>35.94688631100801</v>
       </c>
       <c r="D16" t="n">
-        <v>1.30258649527661</v>
+        <v>1.321833618835596</v>
       </c>
       <c r="E16" t="n">
-        <v>11.37005791335553</v>
+        <v>11.66177086212013</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567953705246185</v>
+        <v>0.7571287385837092</v>
       </c>
       <c r="G16" t="n">
-        <v>21.98666082486014</v>
+        <v>22.23907172660986</v>
       </c>
       <c r="H16" t="n">
-        <v>36.86608815250476</v>
+        <v>36.79131740667847</v>
       </c>
       <c r="I16" t="n">
-        <v>1.928625428304247</v>
+        <v>2.189371768678782</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729971065778868</v>
+        <v>4.732054616148181</v>
       </c>
       <c r="K16" t="n">
-        <v>21.05921474939523</v>
+        <v>20.30745126234527</v>
       </c>
       <c r="L16" t="n">
-        <v>43.48926801208976</v>
+        <v>43.67275013767514</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93576479735772</v>
+        <v>99.92708771102843</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.73128689613306</v>
+        <v>81.62245855718606</v>
       </c>
       <c r="C17" t="n">
-        <v>36.6963031187173</v>
+        <v>37.32360535547916</v>
       </c>
       <c r="D17" t="n">
-        <v>1.303605668510806</v>
+        <v>1.323030013309901</v>
       </c>
       <c r="E17" t="n">
-        <v>12.17747116915832</v>
+        <v>12.52952595972746</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757387504396879</v>
+        <v>0.7578140174465489</v>
       </c>
       <c r="G17" t="n">
-        <v>22.4865507969802</v>
+        <v>22.74701704112463</v>
       </c>
       <c r="H17" t="n">
-        <v>37.37762012623276</v>
+        <v>37.31243399030932</v>
       </c>
       <c r="I17" t="n">
-        <v>1.894979728373602</v>
+        <v>2.216299926227269</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733671902480496</v>
+        <v>4.736337609040929</v>
       </c>
       <c r="K17" t="n">
-        <v>19.26871310386694</v>
+        <v>18.37754144281394</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9718671703357</v>
+        <v>44.22504334296251</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93688339291992</v>
+        <v>99.9261901412556</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.13748982655892</v>
+        <v>79.19817004622715</v>
       </c>
       <c r="C18" t="n">
-        <v>34.39440969841282</v>
+        <v>35.24091795484787</v>
       </c>
       <c r="D18" t="n">
-        <v>1.210411859606012</v>
+        <v>1.236356003309491</v>
       </c>
       <c r="E18" t="n">
-        <v>11.57028177703687</v>
+        <v>12.01675370202642</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578980721886859</v>
+        <v>0.7584035546870214</v>
       </c>
       <c r="G18" t="n">
-        <v>20.87900384584146</v>
+        <v>21.25682017282417</v>
       </c>
       <c r="H18" t="n">
-        <v>37.40281701535499</v>
+        <v>37.34146099279745</v>
       </c>
       <c r="I18" t="n">
-        <v>1.580214305351597</v>
+        <v>1.848353403788703</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736862951179289</v>
+        <v>4.740022216793882</v>
       </c>
       <c r="K18" t="n">
-        <v>21.86251017344109</v>
+        <v>20.80182995377284</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69044180235792</v>
+        <v>43.89568820453965</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94736167421185</v>
+        <v>99.93843611316036</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.0918008943345</v>
+        <v>78.29218381231708</v>
       </c>
       <c r="C19" t="n">
-        <v>33.58120228949376</v>
+        <v>34.61906294946323</v>
       </c>
       <c r="D19" t="n">
-        <v>1.173056458366279</v>
+        <v>1.204688076172528</v>
       </c>
       <c r="E19" t="n">
-        <v>11.43444571502492</v>
+        <v>11.96584171358113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583330847522038</v>
+        <v>0.7589012337408134</v>
       </c>
       <c r="G19" t="n">
-        <v>20.23464171409467</v>
+        <v>20.71234962340751</v>
       </c>
       <c r="H19" t="n">
-        <v>37.42428519941522</v>
+        <v>37.36596518038895</v>
       </c>
       <c r="I19" t="n">
-        <v>1.327456942979914</v>
+        <v>1.541305274146068</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739581779701276</v>
+        <v>4.743132710880082</v>
       </c>
       <c r="K19" t="n">
-        <v>22.9081991056655</v>
+        <v>21.70781618768292</v>
       </c>
       <c r="L19" t="n">
-        <v>43.46637542295989</v>
+        <v>43.62177771274859</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95577681811915</v>
+        <v>99.94865684989473</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.31770585887541</v>
+        <v>75.68350344754654</v>
       </c>
       <c r="C20" t="n">
-        <v>31.01075095663732</v>
+        <v>32.24717045909617</v>
       </c>
       <c r="D20" t="n">
-        <v>1.074504398330038</v>
+        <v>1.112567186106875</v>
       </c>
       <c r="E20" t="n">
-        <v>10.65826350891105</v>
+        <v>11.2650211054874</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587095294518502</v>
+        <v>0.7593307859373051</v>
       </c>
       <c r="G20" t="n">
-        <v>18.53466759026045</v>
+        <v>19.12850387910379</v>
       </c>
       <c r="H20" t="n">
-        <v>37.44286301711122</v>
+        <v>37.38711501083282</v>
       </c>
       <c r="I20" t="n">
-        <v>1.106763255736741</v>
+        <v>1.285148067970198</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741934559074066</v>
+        <v>4.745817412108154</v>
       </c>
       <c r="K20" t="n">
-        <v>25.68229414112458</v>
+        <v>24.31649655245346</v>
       </c>
       <c r="L20" t="n">
-        <v>43.27008109826642</v>
+        <v>43.39351895305742</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96312619602833</v>
+        <v>99.95718596460705</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.51860107348502</v>
+        <v>81.81764963574442</v>
       </c>
       <c r="C21" t="n">
-        <v>34.95508076728571</v>
+        <v>36.00005136556145</v>
       </c>
       <c r="D21" t="n">
-        <v>1.075167015264974</v>
+        <v>1.113434970761306</v>
       </c>
       <c r="E21" t="n">
-        <v>12.75464941256209</v>
+        <v>13.30211947530809</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591774044867905</v>
+        <v>0.7599230518354022</v>
       </c>
       <c r="G21" t="n">
-        <v>20.38764275969854</v>
+        <v>20.85265333334993</v>
       </c>
       <c r="H21" t="n">
-        <v>39.30749834403063</v>
+        <v>39.12550589045011</v>
       </c>
       <c r="I21" t="n">
-        <v>1.48960735939956</v>
+        <v>1.914493840068329</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744858778042442</v>
+        <v>4.749519073971261</v>
       </c>
       <c r="K21" t="n">
-        <v>19.48139892651497</v>
+        <v>18.18235036425559</v>
       </c>
       <c r="L21" t="n">
-        <v>45.51389732866081</v>
+        <v>45.75383154587492</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95037702246148</v>
+        <v>99.93623327569196</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_96_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32497404946396</v>
+        <v>43.93897267249928</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0264200128927</v>
+        <v>95.97870057365097</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02310171093043</v>
+        <v>81.47552588199399</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94297568372332</v>
+        <v>43.23108143754954</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228708982292671</v>
+        <v>2.180380817190384</v>
       </c>
       <c r="E3" t="n">
-        <v>5.714213346005715</v>
+        <v>4.146212478669533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429029940975571</v>
+        <v>0.7376320080272055</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97814241909069</v>
+        <v>32.79656145857203</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17353772848762</v>
+        <v>33.93107236925145</v>
       </c>
       <c r="I3" t="n">
-        <v>6.542452527846453</v>
+        <v>3.073466700113356</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643143713109732</v>
+        <v>4.610200050170034</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97689828906955</v>
+        <v>18.52447411800601</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84528325213594</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7651572249288</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0134251521277</v>
+        <v>88.5116447729397</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56296514488478</v>
+        <v>42.77240089857061</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179582355778925</v>
+        <v>2.186115655125633</v>
       </c>
       <c r="E4" t="n">
-        <v>6.498832782283176</v>
+        <v>6.491304924439246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444578563935259</v>
+        <v>0.7395721278395505</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22917450739126</v>
+        <v>33.46790816608839</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24506139410219</v>
+        <v>34.02031788061932</v>
       </c>
       <c r="I4" t="n">
-        <v>5.463454653719092</v>
+        <v>6.984100219830364</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652861602459536</v>
+        <v>4.62232579899719</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9865748478723</v>
+        <v>11.48835522706031</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26872521480273</v>
+        <v>45.50705124679013</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81826520755982</v>
+        <v>99.76780737242105</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82436264286888</v>
+        <v>87.37840804119953</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22179813893793</v>
+        <v>42.72167806117353</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121491523926747</v>
+        <v>2.132067402745176</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0857814206083</v>
+        <v>7.302990070636104</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457766080323117</v>
+        <v>0.7412178241227396</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34354135672018</v>
+        <v>32.64046706389167</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30572396948634</v>
+        <v>34.09601990964602</v>
       </c>
       <c r="I5" t="n">
-        <v>4.560943963893049</v>
+        <v>5.833034369390697</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661103800201947</v>
+        <v>4.632611400767122</v>
       </c>
       <c r="K5" t="n">
-        <v>14.17563735713113</v>
+        <v>12.62159195880048</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45080187466097</v>
+        <v>44.46272719614181</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84823737073002</v>
+        <v>99.80599721611583</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.24329228596267</v>
+        <v>86.01848294911508</v>
       </c>
       <c r="C6" t="n">
-        <v>41.34898499181093</v>
+        <v>42.26696093172663</v>
       </c>
       <c r="D6" t="n">
-        <v>2.043839327780948</v>
+        <v>2.067050347455124</v>
       </c>
       <c r="E6" t="n">
-        <v>7.460841632292173</v>
+        <v>7.891959123186052</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468998654258047</v>
+        <v>0.7426166541307135</v>
       </c>
       <c r="G6" t="n">
-        <v>31.15968227024453</v>
+        <v>31.64510122833989</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35739380958701</v>
+        <v>34.16036609001282</v>
       </c>
       <c r="I6" t="n">
-        <v>3.806511221720925</v>
+        <v>4.870035417673524</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668124158911278</v>
+        <v>4.64135408831696</v>
       </c>
       <c r="K6" t="n">
-        <v>15.75670771403733</v>
+        <v>13.98151705088491</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76761440626583</v>
+        <v>43.58949328490539</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87330711211409</v>
+        <v>99.83797126751693</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.54620925589816</v>
+        <v>84.49987257682639</v>
       </c>
       <c r="C7" t="n">
-        <v>40.24286217980686</v>
+        <v>41.5045107888333</v>
       </c>
       <c r="D7" t="n">
-        <v>1.961053898255083</v>
+        <v>1.994793546077591</v>
       </c>
       <c r="E7" t="n">
-        <v>7.688001463746533</v>
+        <v>8.293562429010796</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478578235410976</v>
+        <v>0.7438074411276364</v>
       </c>
       <c r="G7" t="n">
-        <v>29.89756364596285</v>
+        <v>30.53889992228887</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40145988289049</v>
+        <v>34.21514229187127</v>
       </c>
       <c r="I7" t="n">
-        <v>3.176161144370254</v>
+        <v>4.064870439402489</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674111397131859</v>
+        <v>4.648796507047727</v>
       </c>
       <c r="K7" t="n">
-        <v>17.45379074410183</v>
+        <v>15.50012742317361</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19761065326572</v>
+        <v>42.86008302639105</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89426357717441</v>
+        <v>99.86472123839796</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.40522777055082</v>
+        <v>82.86740867285373</v>
       </c>
       <c r="C8" t="n">
-        <v>42.52797187313445</v>
+        <v>40.50316477333814</v>
       </c>
       <c r="D8" t="n">
-        <v>1.965261895507815</v>
+        <v>1.917645342206918</v>
       </c>
       <c r="E8" t="n">
-        <v>9.509277847591511</v>
+        <v>8.538146368050311</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494625645784017</v>
+        <v>0.7448223174722655</v>
       </c>
       <c r="G8" t="n">
-        <v>30.39522538915726</v>
+        <v>29.3578146506709</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47527797060647</v>
+        <v>34.26182660372421</v>
       </c>
       <c r="I8" t="n">
-        <v>5.626581074494349</v>
+        <v>3.392013906527471</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684141028615009</v>
+        <v>4.655139484201658</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59477222944919</v>
+        <v>17.13259132714626</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69010478072622</v>
+        <v>42.25133083175441</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81284888330985</v>
+        <v>99.88708693223882</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.24228797527562</v>
+        <v>81.00796687880708</v>
       </c>
       <c r="C9" t="n">
-        <v>41.23775749523958</v>
+        <v>39.17009992692698</v>
       </c>
       <c r="D9" t="n">
-        <v>1.867162409588013</v>
+        <v>1.830213025822754</v>
       </c>
       <c r="E9" t="n">
-        <v>9.817510676659559</v>
+        <v>8.620523353576187</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508392475737958</v>
+        <v>0.7456896497439961</v>
       </c>
       <c r="G9" t="n">
-        <v>28.87799453462916</v>
+        <v>28.01928677881161</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5386053883946</v>
+        <v>34.30172388822382</v>
       </c>
       <c r="I9" t="n">
-        <v>4.697430421094271</v>
+        <v>2.829969871728747</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692745297336223</v>
+        <v>4.660560310899974</v>
       </c>
       <c r="K9" t="n">
-        <v>14.75771202472437</v>
+        <v>18.99203312119293</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84823656130011</v>
+        <v>41.74364434336543</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84370608126405</v>
+        <v>99.90577739148534</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.9546561224513</v>
+        <v>85.80503757149691</v>
       </c>
       <c r="C10" t="n">
-        <v>39.67829590744485</v>
+        <v>42.41460167003277</v>
       </c>
       <c r="D10" t="n">
-        <v>1.764634868856695</v>
+        <v>1.83233253183719</v>
       </c>
       <c r="E10" t="n">
-        <v>9.931871214047055</v>
+        <v>10.48022274372153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520221467203041</v>
+        <v>0.7465532069776273</v>
       </c>
       <c r="G10" t="n">
-        <v>27.29227829179773</v>
+        <v>29.40461206167727</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59301874913398</v>
+        <v>35.69432464287929</v>
       </c>
       <c r="I10" t="n">
-        <v>3.920692434893639</v>
+        <v>2.981034840793835</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700138417001899</v>
+        <v>4.665957543610169</v>
       </c>
       <c r="K10" t="n">
-        <v>17.0453438775487</v>
+        <v>14.19496242850308</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14587603664272</v>
+        <v>43.29118301475184</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86951582163627</v>
+        <v>99.90074711328769</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.4666698485548</v>
+        <v>85.56660050656652</v>
       </c>
       <c r="C11" t="n">
-        <v>37.79736086348274</v>
+        <v>42.55058055710408</v>
       </c>
       <c r="D11" t="n">
-        <v>1.654267430045098</v>
+        <v>1.816445308714025</v>
       </c>
       <c r="E11" t="n">
-        <v>9.855970237116342</v>
+        <v>10.8460252392288</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530413553050038</v>
+        <v>0.747292029729794</v>
       </c>
       <c r="G11" t="n">
-        <v>25.58530825082226</v>
+        <v>29.18292795463438</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63990234403016</v>
+        <v>35.76291768131119</v>
       </c>
       <c r="I11" t="n">
-        <v>3.271671760579667</v>
+        <v>2.540417107137102</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706508470656273</v>
+        <v>4.670575185811211</v>
       </c>
       <c r="K11" t="n">
-        <v>19.53333015144519</v>
+        <v>14.4333994934335</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56040086188057</v>
+        <v>42.93142310008526</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8910918768085</v>
+        <v>99.91540315062284</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.98894512339831</v>
+        <v>83.76537817610786</v>
       </c>
       <c r="C12" t="n">
-        <v>35.82526140376828</v>
+        <v>41.14430391117293</v>
       </c>
       <c r="D12" t="n">
-        <v>1.545574903309589</v>
+        <v>1.739722586620072</v>
       </c>
       <c r="E12" t="n">
-        <v>9.66331933431721</v>
+        <v>10.74104578793232</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539198909362799</v>
+        <v>0.7479221077719667</v>
       </c>
       <c r="G12" t="n">
-        <v>23.90424281328722</v>
+        <v>27.95030418082178</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68031498306886</v>
+        <v>35.79307112636155</v>
       </c>
       <c r="I12" t="n">
-        <v>2.729573880127398</v>
+        <v>2.118799213025371</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711999318351747</v>
+        <v>4.67451317357479</v>
       </c>
       <c r="K12" t="n">
-        <v>22.01105487660168</v>
+        <v>16.23462182389217</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07280394850282</v>
+        <v>42.55050712306999</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90912022887278</v>
+        <v>99.92943285813509</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.58233077058007</v>
+        <v>84.95592398209386</v>
       </c>
       <c r="C13" t="n">
-        <v>33.83955007238308</v>
+        <v>42.13170788212148</v>
       </c>
       <c r="D13" t="n">
-        <v>1.441088611448453</v>
+        <v>1.741074660063866</v>
       </c>
       <c r="E13" t="n">
-        <v>9.389533179965891</v>
+        <v>11.39118491653422</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754676955923788</v>
+        <v>0.7485033760889512</v>
       </c>
       <c r="G13" t="n">
-        <v>22.28823204217527</v>
+        <v>28.28368874951657</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71513997249424</v>
+        <v>36.13255091793524</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276929034048759</v>
+        <v>1.980775261399074</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716730974523673</v>
+        <v>4.678146100555944</v>
       </c>
       <c r="K13" t="n">
-        <v>24.41766922941993</v>
+        <v>15.04407601790615</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66695920152678</v>
+        <v>42.75824153188296</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92417850332978</v>
+        <v>99.93402543191058</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.91912147252413</v>
+        <v>83.09751484786281</v>
       </c>
       <c r="C14" t="n">
-        <v>38.29243609150397</v>
+        <v>40.58115024316687</v>
       </c>
       <c r="D14" t="n">
-        <v>1.442911403316687</v>
+        <v>1.664051286594298</v>
       </c>
       <c r="E14" t="n">
-        <v>11.87586213456655</v>
+        <v>11.16254042645257</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556315252732878</v>
+        <v>0.7489993126039959</v>
       </c>
       <c r="G14" t="n">
-        <v>24.26646603821983</v>
+        <v>27.0324471045597</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70909240982182</v>
+        <v>36.156491292761</v>
       </c>
       <c r="I14" t="n">
-        <v>3.146460928367901</v>
+        <v>1.651739721116276</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722697032958047</v>
+        <v>4.681245703774973</v>
       </c>
       <c r="K14" t="n">
-        <v>17.08087852747587</v>
+        <v>16.90248515213719</v>
       </c>
       <c r="L14" t="n">
-        <v>44.5219358447743</v>
+        <v>42.46134306965708</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89525046375414</v>
+        <v>99.94497846496114</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.17984581627219</v>
+        <v>82.26608253461322</v>
       </c>
       <c r="C15" t="n">
-        <v>38.02913331454411</v>
+        <v>39.98365344405777</v>
       </c>
       <c r="D15" t="n">
-        <v>1.414944448012835</v>
+        <v>1.629179138373699</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09263490966493</v>
+        <v>11.16176321701364</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564360265265502</v>
+        <v>0.7494238542486379</v>
       </c>
       <c r="G15" t="n">
-        <v>23.80560656056333</v>
+        <v>26.46595044079099</v>
       </c>
       <c r="H15" t="n">
-        <v>36.75765630273722</v>
+        <v>36.17698521848244</v>
       </c>
       <c r="I15" t="n">
-        <v>2.624842402976382</v>
+        <v>1.398881576649834</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727725165790937</v>
+        <v>4.683899089053986</v>
       </c>
       <c r="K15" t="n">
-        <v>17.82015418372781</v>
+        <v>17.73391746538677</v>
       </c>
       <c r="L15" t="n">
-        <v>44.06331080927342</v>
+        <v>42.23582611978064</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91259830754534</v>
+        <v>99.95339702922517</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.69254873765473</v>
+        <v>79.99032263382983</v>
       </c>
       <c r="C16" t="n">
-        <v>35.94688631100801</v>
+        <v>37.9248458575116</v>
       </c>
       <c r="D16" t="n">
-        <v>1.321833618835596</v>
+        <v>1.535479961761194</v>
       </c>
       <c r="E16" t="n">
-        <v>11.66177086212013</v>
+        <v>10.71419891641931</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571287385837092</v>
+        <v>0.7497880874553687</v>
       </c>
       <c r="G16" t="n">
-        <v>22.23907172660986</v>
+        <v>24.94381103563943</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79131740667847</v>
+        <v>36.19456787115793</v>
       </c>
       <c r="I16" t="n">
-        <v>2.189371768678782</v>
+        <v>1.166301214800543</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732054616148181</v>
+        <v>4.686175546596054</v>
       </c>
       <c r="K16" t="n">
-        <v>20.30745126234527</v>
+        <v>20.00967736617017</v>
       </c>
       <c r="L16" t="n">
-        <v>43.67275013767514</v>
+        <v>42.02661895474462</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92708771102843</v>
+        <v>99.9611421784264</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.62245855718606</v>
+        <v>84.49630897687366</v>
       </c>
       <c r="C17" t="n">
-        <v>37.32360535547916</v>
+        <v>40.87879481163785</v>
       </c>
       <c r="D17" t="n">
-        <v>1.323030013309901</v>
+        <v>1.536289535328759</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52952595972746</v>
+        <v>12.29975575656203</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578140174465489</v>
+        <v>0.7501834091997066</v>
       </c>
       <c r="G17" t="n">
-        <v>22.74701704112463</v>
+        <v>26.3141192356793</v>
       </c>
       <c r="H17" t="n">
-        <v>37.31243399030932</v>
+        <v>37.57080797234661</v>
       </c>
       <c r="I17" t="n">
-        <v>2.216299926227269</v>
+        <v>1.336506760259081</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736337609040929</v>
+        <v>4.688646307498166</v>
       </c>
       <c r="K17" t="n">
-        <v>18.37754144281394</v>
+        <v>15.50369102312633</v>
       </c>
       <c r="L17" t="n">
-        <v>44.22504334296251</v>
+        <v>43.57298741638317</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9261901412556</v>
+        <v>99.95547325114735</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.19817004622715</v>
+        <v>86.02302483174786</v>
       </c>
       <c r="C18" t="n">
-        <v>35.24091795484787</v>
+        <v>41.63025118955213</v>
       </c>
       <c r="D18" t="n">
-        <v>1.236356003309491</v>
+        <v>1.537519521164381</v>
       </c>
       <c r="E18" t="n">
-        <v>12.01675370202642</v>
+        <v>12.91138136946313</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584035546870214</v>
+        <v>0.7507840218747365</v>
       </c>
       <c r="G18" t="n">
-        <v>21.25682017282417</v>
+        <v>26.46389633503636</v>
       </c>
       <c r="H18" t="n">
-        <v>37.34146099279745</v>
+        <v>37.60088795439177</v>
       </c>
       <c r="I18" t="n">
-        <v>1.848353403788703</v>
+        <v>2.066155493100379</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740022216793882</v>
+        <v>4.692400136717103</v>
       </c>
       <c r="K18" t="n">
-        <v>20.80182995377284</v>
+        <v>13.97697516825212</v>
       </c>
       <c r="L18" t="n">
-        <v>43.89568820453965</v>
+        <v>44.32395688857152</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93843611316036</v>
+        <v>99.93118324637578</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.29218381231708</v>
+        <v>83.42084363677947</v>
       </c>
       <c r="C19" t="n">
-        <v>34.61906294946323</v>
+        <v>39.34836609327858</v>
       </c>
       <c r="D19" t="n">
-        <v>1.204688076172528</v>
+        <v>1.440719705373902</v>
       </c>
       <c r="E19" t="n">
-        <v>11.96584171358113</v>
+        <v>12.38566467203263</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589012337408134</v>
+        <v>0.7513009139109388</v>
       </c>
       <c r="G19" t="n">
-        <v>20.71234962340751</v>
+        <v>24.79777095902172</v>
       </c>
       <c r="H19" t="n">
-        <v>37.36596518038895</v>
+        <v>37.62677502573518</v>
       </c>
       <c r="I19" t="n">
-        <v>1.541305274146068</v>
+        <v>1.722981648761714</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743132710880082</v>
+        <v>4.695630711943367</v>
       </c>
       <c r="K19" t="n">
-        <v>21.70781618768292</v>
+        <v>16.57915636322054</v>
       </c>
       <c r="L19" t="n">
-        <v>43.62177771274859</v>
+        <v>44.01508433535919</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94865684989473</v>
+        <v>99.94260679185832</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.68350344754654</v>
+        <v>80.71659995047752</v>
       </c>
       <c r="C20" t="n">
-        <v>32.24717045909617</v>
+        <v>36.91051557080973</v>
       </c>
       <c r="D20" t="n">
-        <v>1.112567186106875</v>
+        <v>1.34064363507927</v>
       </c>
       <c r="E20" t="n">
-        <v>11.2650211054874</v>
+        <v>11.76476975602564</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593307859373051</v>
+        <v>0.7517466592371715</v>
       </c>
       <c r="G20" t="n">
-        <v>19.12850387910379</v>
+        <v>23.0752544553683</v>
       </c>
       <c r="H20" t="n">
-        <v>37.38711501083282</v>
+        <v>37.64909891593468</v>
       </c>
       <c r="I20" t="n">
-        <v>1.285148067970198</v>
+        <v>1.436669908600158</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745817412108154</v>
+        <v>4.698416620232321</v>
       </c>
       <c r="K20" t="n">
-        <v>24.31649655245346</v>
+        <v>19.28340004952247</v>
       </c>
       <c r="L20" t="n">
-        <v>43.39351895305742</v>
+        <v>43.75822377831331</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95718596460705</v>
+        <v>99.9521393986455</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.81764963574442</v>
+        <v>78.01845291741898</v>
       </c>
       <c r="C21" t="n">
-        <v>36.00005136556145</v>
+        <v>34.4338049599574</v>
       </c>
       <c r="D21" t="n">
-        <v>1.113434970761306</v>
+        <v>1.241301051798341</v>
       </c>
       <c r="E21" t="n">
-        <v>13.30211947530809</v>
+        <v>11.0926321133029</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599230518354022</v>
+        <v>0.7521313846476462</v>
       </c>
       <c r="G21" t="n">
-        <v>20.85265333334993</v>
+        <v>21.36536278283184</v>
       </c>
       <c r="H21" t="n">
-        <v>39.12550589045011</v>
+        <v>37.66836679675124</v>
       </c>
       <c r="I21" t="n">
-        <v>1.914493840068329</v>
+        <v>1.197837634039214</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749519073971261</v>
+        <v>4.700821154047788</v>
       </c>
       <c r="K21" t="n">
-        <v>18.18235036425559</v>
+        <v>21.98154708258102</v>
       </c>
       <c r="L21" t="n">
-        <v>45.75383154587492</v>
+        <v>43.54474046000047</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93623327569196</v>
+        <v>99.96009250253888</v>
       </c>
     </row>
   </sheetData>
